--- a/owlcms/src/main/resources/templates/credentials/Coaches_A4.xlsx
+++ b/owlcms/src/main/resources/templates/credentials/Coaches_A4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\credentials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D104617A-A02A-4944-B083-B2CDFCAD48DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BE8124-7743-463A-B1A7-461E9400CB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>${competition.competitionName}</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>${coach.fullName}</t>
+  </si>
+  <si>
+    <t>X ${coach.teamFlagPath}</t>
   </si>
 </sst>
 </file>
@@ -1066,6 +1069,9 @@
     </row>
     <row r="10" spans="1:9" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="29"/>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
       <c r="E10" s="37"/>
       <c r="F10" s="38"/>
       <c r="G10" s="39"/>

--- a/owlcms/src/main/resources/templates/credentials/Coaches_A4.xlsx
+++ b/owlcms/src/main/resources/templates/credentials/Coaches_A4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\credentials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BE8124-7743-463A-B1A7-461E9400CB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA8177D-98AA-42AA-8510-EFB675754AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>${competition.competitionName}</t>
   </si>
@@ -205,9 +205,6 @@
   </si>
   <si>
     <t>${coach.fullName}</t>
-  </si>
-  <si>
-    <t>X ${coach.teamFlagPath}</t>
   </si>
 </sst>
 </file>
@@ -1069,9 +1066,6 @@
     </row>
     <row r="10" spans="1:9" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="29"/>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
       <c r="E10" s="37"/>
       <c r="F10" s="38"/>
       <c r="G10" s="39"/>

--- a/owlcms/src/main/resources/templates/credentials/Coaches_A4.xlsx
+++ b/owlcms/src/main/resources/templates/credentials/Coaches_A4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\credentials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA8177D-98AA-42AA-8510-EFB675754AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48506CEE-D11D-45E2-9082-19811E32945C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6735" yWindow="3555" windowWidth="19620" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">jx:image(src="local.getBytes('pictures/'+coach.membershipId+'.jpg')" imageType="JPEG" ptHeight="300" lastCell="G12")
+          <t xml:space="preserve">jx:image(src="local.getBytes('pictures/'+coach.membershipId+'.jpg')" imageType="JPEG" ptHeight="260" lastCell="G12")
 </t>
         </r>
       </text>
@@ -197,14 +197,14 @@
     <t>Federation Logo</t>
   </si>
   <si>
-    <t>COACH</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 ${coach.team}</t>
   </si>
   <si>
     <t>${coach.fullName}</t>
+  </si>
+  <si>
+    <t>${t.get("Coach")}</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1039,7 @@
     <row r="7" spans="1:9" s="26" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="27"/>
       <c r="C7" s="35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="35"/>
       <c r="E7" s="35"/>
@@ -1050,7 +1050,7 @@
     <row r="8" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11"/>
       <c r="C8" s="36" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" s="36"/>
       <c r="E8" s="36"/>
@@ -1084,7 +1084,7 @@
     <row r="12" spans="1:9" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="29"/>
       <c r="C12" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="42"/>
       <c r="F12" s="43"/>

--- a/owlcms/src/main/resources/templates/credentials/Coaches_A4.xlsx
+++ b/owlcms/src/main/resources/templates/credentials/Coaches_A4.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\credentials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\credentials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48506CEE-D11D-45E2-9082-19811E32945C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A2B9C1-04DC-450C-8F23-8DC5FF6FEC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6735" yWindow="3555" windowWidth="19620" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -168,7 +168,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:image(src="local.getBytes('logos/liveQR.png')" imageType="PNG" ptHeight="100" lastCell="G19")</t>
+          <t>jx:image(src="local.getBytes('logos/sponsors.png')" imageType="PNG" ptHeight="100" lastCell="G19")</t>
         </r>
       </text>
     </comment>
